--- a/project4/data/5_PAproject_5_4_rater.xlsx
+++ b/project4/data/5_PAproject_5_4_rater.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\aiagent\project4\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB689315-4A21-4180-8819-F041A34B0026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CEBBBDC-4947-4298-83E2-E8EBE4B1FC51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6915" yWindow="2265" windowWidth="28830" windowHeight="13335" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="rating_data" sheetId="2" r:id="rId1"/>
@@ -19,6 +19,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">rating_data!$A$1:$I$501</definedName>
   </definedNames>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -2051,7 +2056,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I501"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -2064,7 +2069,7 @@
     <col min="9" max="9" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2093,7 +2098,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -2122,7 +2127,7 @@
         <v>4.4800000000000004</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -2151,7 +2156,7 @@
         <v>3.83</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
@@ -2180,7 +2185,7 @@
         <v>4.93</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -2209,7 +2214,7 @@
         <v>3.79</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
         <v>21</v>
       </c>
@@ -2238,7 +2243,7 @@
         <v>4.6399999999999997</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -2264,10 +2269,10 @@
         <v>66</v>
       </c>
       <c r="I7" s="8">
-        <v>3.71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>28</v>
       </c>
@@ -2296,7 +2301,7 @@
         <v>3.84</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -2325,7 +2330,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
         <v>34</v>
       </c>
@@ -2351,10 +2356,10 @@
         <v>66.7</v>
       </c>
       <c r="I10" s="5">
-        <v>4.97</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>36</v>
       </c>
@@ -2383,7 +2388,7 @@
         <v>4.0599999999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
         <v>37</v>
       </c>
@@ -2409,10 +2414,10 @@
         <v>73.599999999999994</v>
       </c>
       <c r="I12" s="5">
-        <v>4.55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -2441,7 +2446,7 @@
         <v>4.41</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
         <v>40</v>
       </c>
@@ -2467,10 +2472,10 @@
         <v>71.099999999999994</v>
       </c>
       <c r="I14" s="5">
-        <v>3.59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -2499,7 +2504,7 @@
         <v>3.72</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A16" s="2" t="s">
         <v>43</v>
       </c>
@@ -2525,10 +2530,10 @@
         <v>66.3</v>
       </c>
       <c r="I16" s="5">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>45</v>
       </c>
@@ -2557,7 +2562,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A18" s="2" t="s">
         <v>48</v>
       </c>
@@ -2583,10 +2588,10 @@
         <v>63.8</v>
       </c>
       <c r="I18" s="5">
-        <v>4.32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -2615,7 +2620,7 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A20" s="2" t="s">
         <v>52</v>
       </c>
@@ -2644,7 +2649,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>54</v>
       </c>
@@ -2673,7 +2678,7 @@
         <v>3.19</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A22" s="2" t="s">
         <v>55</v>
       </c>
@@ -2702,7 +2707,7 @@
         <v>4.68</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>57</v>
       </c>
@@ -2731,7 +2736,7 @@
         <v>4.5599999999999996</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A24" s="2" t="s">
         <v>58</v>
       </c>
@@ -2760,7 +2765,7 @@
         <v>4.41</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>60</v>
       </c>
@@ -2789,7 +2794,7 @@
         <v>4.6399999999999997</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A26" s="2" t="s">
         <v>61</v>
       </c>
@@ -2818,7 +2823,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>62</v>
       </c>
@@ -2847,7 +2852,7 @@
         <v>3.26</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A28" s="2" t="s">
         <v>64</v>
       </c>
@@ -2876,7 +2881,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>65</v>
       </c>
@@ -2905,7 +2910,7 @@
         <v>3.52</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A30" s="2" t="s">
         <v>66</v>
       </c>
@@ -2934,7 +2939,7 @@
         <v>4.74</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
         <v>67</v>
       </c>
@@ -2963,7 +2968,7 @@
         <v>3.47</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A32" s="2" t="s">
         <v>68</v>
       </c>
@@ -2992,7 +2997,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>70</v>
       </c>
@@ -3021,7 +3026,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A34" s="2" t="s">
         <v>71</v>
       </c>
@@ -3050,7 +3055,7 @@
         <v>4.03</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
         <v>73</v>
       </c>
@@ -3079,7 +3084,7 @@
         <v>3.73</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A36" s="2" t="s">
         <v>74</v>
       </c>
@@ -3108,7 +3113,7 @@
         <v>4.03</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
         <v>76</v>
       </c>
@@ -3137,7 +3142,7 @@
         <v>4.49</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A38" s="2" t="s">
         <v>77</v>
       </c>
@@ -3166,7 +3171,7 @@
         <v>3.83</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
         <v>78</v>
       </c>
@@ -3195,7 +3200,7 @@
         <v>3.58</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A40" s="2" t="s">
         <v>79</v>
       </c>
@@ -3224,7 +3229,7 @@
         <v>4.3099999999999996</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
         <v>80</v>
       </c>
@@ -3253,7 +3258,7 @@
         <v>3.83</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A42" s="2" t="s">
         <v>81</v>
       </c>
@@ -3282,7 +3287,7 @@
         <v>4.49</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
         <v>82</v>
       </c>
@@ -3311,7 +3316,7 @@
         <v>4.1399999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A44" s="2" t="s">
         <v>83</v>
       </c>
@@ -3340,7 +3345,7 @@
         <v>3.82</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
         <v>85</v>
       </c>
@@ -3369,7 +3374,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A46" s="2" t="s">
         <v>86</v>
       </c>
@@ -3398,7 +3403,7 @@
         <v>3.71</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
         <v>87</v>
       </c>
@@ -3427,7 +3432,7 @@
         <v>3.62</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A48" s="2" t="s">
         <v>88</v>
       </c>
@@ -3456,7 +3461,7 @@
         <v>4.54</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
         <v>89</v>
       </c>
@@ -3485,7 +3490,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A50" s="2" t="s">
         <v>90</v>
       </c>
@@ -3514,7 +3519,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
         <v>91</v>
       </c>
@@ -3543,7 +3548,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A52" s="2" t="s">
         <v>93</v>
       </c>
@@ -3572,7 +3577,7 @@
         <v>3.35</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
         <v>94</v>
       </c>
@@ -3601,7 +3606,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A54" s="2" t="s">
         <v>95</v>
       </c>
@@ -3630,7 +3635,7 @@
         <v>3.51</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
         <v>96</v>
       </c>
@@ -3659,7 +3664,7 @@
         <v>3.74</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A56" s="2" t="s">
         <v>97</v>
       </c>
@@ -3688,7 +3693,7 @@
         <v>3.79</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
         <v>98</v>
       </c>
@@ -3717,7 +3722,7 @@
         <v>3.91</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A58" s="2" t="s">
         <v>100</v>
       </c>
@@ -3746,7 +3751,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
         <v>101</v>
       </c>
@@ -3775,7 +3780,7 @@
         <v>4.5599999999999996</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A60" s="2" t="s">
         <v>102</v>
       </c>
@@ -3804,7 +3809,7 @@
         <v>3.84</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
         <v>103</v>
       </c>
@@ -3833,7 +3838,7 @@
         <v>3.43</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A62" s="2" t="s">
         <v>104</v>
       </c>
@@ -3862,7 +3867,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
         <v>105</v>
       </c>
@@ -3891,7 +3896,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A64" s="2" t="s">
         <v>107</v>
       </c>
@@ -3920,7 +3925,7 @@
         <v>4.46</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
         <v>108</v>
       </c>
@@ -3949,7 +3954,7 @@
         <v>4.79</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A66" s="2" t="s">
         <v>109</v>
       </c>
@@ -3978,7 +3983,7 @@
         <v>3.81</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
         <v>110</v>
       </c>
@@ -4007,7 +4012,7 @@
         <v>4.3600000000000003</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A68" s="2" t="s">
         <v>111</v>
       </c>
@@ -4036,7 +4041,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
         <v>112</v>
       </c>
@@ -4065,7 +4070,7 @@
         <v>3.51</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A70" s="2" t="s">
         <v>113</v>
       </c>
@@ -4094,7 +4099,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
         <v>114</v>
       </c>
@@ -4123,7 +4128,7 @@
         <v>3.16</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A72" s="2" t="s">
         <v>115</v>
       </c>
@@ -4152,7 +4157,7 @@
         <v>3.49</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
         <v>116</v>
       </c>
@@ -4181,7 +4186,7 @@
         <v>3.35</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A74" s="2" t="s">
         <v>117</v>
       </c>
@@ -4210,7 +4215,7 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
         <v>118</v>
       </c>
@@ -4239,7 +4244,7 @@
         <v>4.01</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A76" s="2" t="s">
         <v>119</v>
       </c>
@@ -4268,7 +4273,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
         <v>120</v>
       </c>
@@ -4297,7 +4302,7 @@
         <v>3.71</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A78" s="2" t="s">
         <v>121</v>
       </c>
@@ -4326,7 +4331,7 @@
         <v>4.2300000000000004</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
         <v>122</v>
       </c>
@@ -4355,7 +4360,7 @@
         <v>4.2300000000000004</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A80" s="2" t="s">
         <v>123</v>
       </c>
@@ -4384,7 +4389,7 @@
         <v>4.49</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
         <v>124</v>
       </c>
@@ -4413,7 +4418,7 @@
         <v>3.37</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A82" s="2" t="s">
         <v>125</v>
       </c>
@@ -4442,7 +4447,7 @@
         <v>3.76</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
         <v>126</v>
       </c>
@@ -4471,7 +4476,7 @@
         <v>4.7300000000000004</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A84" s="2" t="s">
         <v>127</v>
       </c>
@@ -4500,7 +4505,7 @@
         <v>3.38</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
         <v>129</v>
       </c>
@@ -4529,7 +4534,7 @@
         <v>4.16</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A86" s="2" t="s">
         <v>130</v>
       </c>
@@ -4558,7 +4563,7 @@
         <v>4.5199999999999996</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
         <v>131</v>
       </c>
@@ -4587,7 +4592,7 @@
         <v>4.24</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A88" s="2" t="s">
         <v>132</v>
       </c>
@@ -4616,7 +4621,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
         <v>133</v>
       </c>
@@ -4645,7 +4650,7 @@
         <v>3.77</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A90" s="2" t="s">
         <v>134</v>
       </c>
@@ -4674,7 +4679,7 @@
         <v>4.22</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
         <v>135</v>
       </c>
@@ -4703,7 +4708,7 @@
         <v>3.89</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A92" s="2" t="s">
         <v>136</v>
       </c>
@@ -4732,7 +4737,7 @@
         <v>3.89</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
         <v>137</v>
       </c>
@@ -4761,7 +4766,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A94" s="2" t="s">
         <v>138</v>
       </c>
@@ -4790,7 +4795,7 @@
         <v>3.82</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
         <v>139</v>
       </c>
@@ -4819,7 +4824,7 @@
         <v>3.01</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A96" s="2" t="s">
         <v>140</v>
       </c>
@@ -4848,7 +4853,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
         <v>141</v>
       </c>
@@ -4877,7 +4882,7 @@
         <v>3.93</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A98" s="2" t="s">
         <v>142</v>
       </c>
@@ -4906,7 +4911,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
         <v>143</v>
       </c>
@@ -4935,7 +4940,7 @@
         <v>3.87</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A100" s="2" t="s">
         <v>144</v>
       </c>
@@ -4964,7 +4969,7 @@
         <v>2.89</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
         <v>145</v>
       </c>
@@ -4993,7 +4998,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A102" s="2" t="s">
         <v>146</v>
       </c>
@@ -5022,7 +5027,7 @@
         <v>3.97</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
         <v>147</v>
       </c>
@@ -5051,7 +5056,7 @@
         <v>4.24</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A104" s="2" t="s">
         <v>148</v>
       </c>
@@ -5080,7 +5085,7 @@
         <v>4.68</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
         <v>149</v>
       </c>
@@ -5109,7 +5114,7 @@
         <v>4.03</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A106" s="2" t="s">
         <v>150</v>
       </c>
@@ -5138,7 +5143,7 @@
         <v>4.29</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
         <v>151</v>
       </c>
@@ -5167,7 +5172,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A108" s="2" t="s">
         <v>152</v>
       </c>
@@ -5196,7 +5201,7 @@
         <v>4.13</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
         <v>153</v>
       </c>
@@ -5225,7 +5230,7 @@
         <v>3.53</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A110" s="2" t="s">
         <v>154</v>
       </c>
@@ -5254,7 +5259,7 @@
         <v>4.63</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A111" t="s">
         <v>155</v>
       </c>
@@ -5283,7 +5288,7 @@
         <v>3.84</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A112" s="2" t="s">
         <v>156</v>
       </c>
@@ -5312,7 +5317,7 @@
         <v>4.6500000000000004</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
         <v>157</v>
       </c>
@@ -5341,7 +5346,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A114" s="2" t="s">
         <v>158</v>
       </c>
@@ -5370,7 +5375,7 @@
         <v>3.94</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
         <v>159</v>
       </c>
@@ -5399,7 +5404,7 @@
         <v>4.09</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A116" s="2" t="s">
         <v>160</v>
       </c>
@@ -5428,7 +5433,7 @@
         <v>4.21</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A117" t="s">
         <v>161</v>
       </c>
@@ -5457,7 +5462,7 @@
         <v>3.26</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A118" s="2" t="s">
         <v>162</v>
       </c>
@@ -5486,7 +5491,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
         <v>163</v>
       </c>
@@ -5515,7 +5520,7 @@
         <v>3.83</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A120" s="2" t="s">
         <v>165</v>
       </c>
@@ -5544,7 +5549,7 @@
         <v>3.47</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
         <v>166</v>
       </c>
@@ -5573,7 +5578,7 @@
         <v>4.1100000000000003</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A122" s="2" t="s">
         <v>167</v>
       </c>
@@ -5602,7 +5607,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A123" t="s">
         <v>168</v>
       </c>
@@ -5631,7 +5636,7 @@
         <v>4.29</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A124" s="2" t="s">
         <v>169</v>
       </c>
@@ -5660,7 +5665,7 @@
         <v>3.02</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
         <v>170</v>
       </c>
@@ -5689,7 +5694,7 @@
         <v>4.37</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A126" s="2" t="s">
         <v>171</v>
       </c>
@@ -5718,7 +5723,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
         <v>172</v>
       </c>
@@ -5747,7 +5752,7 @@
         <v>3.91</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A128" s="2" t="s">
         <v>173</v>
       </c>
@@ -5776,7 +5781,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A129" t="s">
         <v>174</v>
       </c>
@@ -5805,7 +5810,7 @@
         <v>4.12</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A130" s="2" t="s">
         <v>175</v>
       </c>
@@ -5834,7 +5839,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
         <v>176</v>
       </c>
@@ -5863,7 +5868,7 @@
         <v>3.65</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A132" s="2" t="s">
         <v>177</v>
       </c>
@@ -5892,7 +5897,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
         <v>178</v>
       </c>
@@ -5921,7 +5926,7 @@
         <v>3.35</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A134" s="2" t="s">
         <v>179</v>
       </c>
@@ -5950,7 +5955,7 @@
         <v>3.49</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A135" t="s">
         <v>180</v>
       </c>
@@ -5979,7 +5984,7 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A136" s="2" t="s">
         <v>181</v>
       </c>
@@ -6008,7 +6013,7 @@
         <v>4.5599999999999996</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A137" t="s">
         <v>182</v>
       </c>
@@ -6037,7 +6042,7 @@
         <v>4.12</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A138" s="2" t="s">
         <v>183</v>
       </c>
@@ -6066,7 +6071,7 @@
         <v>3.73</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A139" t="s">
         <v>184</v>
       </c>
@@ -6095,7 +6100,7 @@
         <v>4.4800000000000004</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A140" s="2" t="s">
         <v>185</v>
       </c>
@@ -6124,7 +6129,7 @@
         <v>4.92</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A141" t="s">
         <v>186</v>
       </c>
@@ -6153,7 +6158,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A142" s="2" t="s">
         <v>187</v>
       </c>
@@ -6182,7 +6187,7 @@
         <v>4.58</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A143" t="s">
         <v>188</v>
       </c>
@@ -6211,7 +6216,7 @@
         <v>3.65</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A144" s="2" t="s">
         <v>189</v>
       </c>
@@ -6240,7 +6245,7 @@
         <v>4.05</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A145" t="s">
         <v>190</v>
       </c>
@@ -6269,7 +6274,7 @@
         <v>3.99</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A146" s="2" t="s">
         <v>191</v>
       </c>
@@ -6298,7 +6303,7 @@
         <v>4.24</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
         <v>192</v>
       </c>
@@ -6327,7 +6332,7 @@
         <v>4.03</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A148" s="2" t="s">
         <v>193</v>
       </c>
@@ -6356,7 +6361,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A149" t="s">
         <v>194</v>
       </c>
@@ -6385,7 +6390,7 @@
         <v>3.88</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A150" s="2" t="s">
         <v>195</v>
       </c>
@@ -6414,7 +6419,7 @@
         <v>4.29</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A151" t="s">
         <v>196</v>
       </c>
@@ -6443,7 +6448,7 @@
         <v>4.68</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A152" s="2" t="s">
         <v>197</v>
       </c>
@@ -6472,7 +6477,7 @@
         <v>3.28</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
         <v>198</v>
       </c>
@@ -6501,7 +6506,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A154" s="2" t="s">
         <v>199</v>
       </c>
@@ -6530,7 +6535,7 @@
         <v>3.52</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A155" t="s">
         <v>200</v>
       </c>
@@ -6559,7 +6564,7 @@
         <v>4.41</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A156" s="2" t="s">
         <v>201</v>
       </c>
@@ -6588,7 +6593,7 @@
         <v>3.88</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A157" t="s">
         <v>202</v>
       </c>
@@ -6617,7 +6622,7 @@
         <v>3.77</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A158" s="2" t="s">
         <v>203</v>
       </c>
@@ -6646,7 +6651,7 @@
         <v>3.99</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A159" t="s">
         <v>204</v>
       </c>
@@ -6675,7 +6680,7 @@
         <v>4.84</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A160" s="2" t="s">
         <v>205</v>
       </c>
@@ -6704,7 +6709,7 @@
         <v>4.1100000000000003</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A161" t="s">
         <v>206</v>
       </c>
@@ -6733,7 +6738,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A162" s="2" t="s">
         <v>207</v>
       </c>
@@ -6762,7 +6767,7 @@
         <v>3.42</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A163" t="s">
         <v>208</v>
       </c>
@@ -6791,7 +6796,7 @@
         <v>4.26</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A164" s="2" t="s">
         <v>209</v>
       </c>
@@ -6820,7 +6825,7 @@
         <v>2.83</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A165" t="s">
         <v>210</v>
       </c>
@@ -6849,7 +6854,7 @@
         <v>4.3600000000000003</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A166" s="2" t="s">
         <v>211</v>
       </c>
@@ -6878,7 +6883,7 @@
         <v>4.67</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A167" t="s">
         <v>212</v>
       </c>
@@ -6907,7 +6912,7 @@
         <v>4.62</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A168" s="2" t="s">
         <v>213</v>
       </c>
@@ -6936,7 +6941,7 @@
         <v>3.53</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A169" t="s">
         <v>214</v>
       </c>
@@ -6965,7 +6970,7 @@
         <v>3.86</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A170" s="2" t="s">
         <v>215</v>
       </c>
@@ -6994,7 +6999,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A171" t="s">
         <v>216</v>
       </c>
@@ -7023,7 +7028,7 @@
         <v>4.3600000000000003</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A172" s="2" t="s">
         <v>217</v>
       </c>
@@ -7052,7 +7057,7 @@
         <v>4.3099999999999996</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A173" t="s">
         <v>218</v>
       </c>
@@ -7081,7 +7086,7 @@
         <v>4.49</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A174" s="2" t="s">
         <v>219</v>
       </c>
@@ -7110,7 +7115,7 @@
         <v>4.03</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A175" t="s">
         <v>220</v>
       </c>
@@ -7139,7 +7144,7 @@
         <v>4.1100000000000003</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A176" s="2" t="s">
         <v>221</v>
       </c>
@@ -7168,7 +7173,7 @@
         <v>3.28</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A177" t="s">
         <v>222</v>
       </c>
@@ -7197,7 +7202,7 @@
         <v>4.2699999999999996</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A178" s="2" t="s">
         <v>223</v>
       </c>
@@ -7226,7 +7231,7 @@
         <v>3.67</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A179" t="s">
         <v>224</v>
       </c>
@@ -7255,7 +7260,7 @@
         <v>4.24</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A180" s="2" t="s">
         <v>225</v>
       </c>
@@ -7284,7 +7289,7 @@
         <v>4.91</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A181" t="s">
         <v>226</v>
       </c>
@@ -7313,7 +7318,7 @@
         <v>3.64</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A182" s="2" t="s">
         <v>227</v>
       </c>
@@ -7342,7 +7347,7 @@
         <v>3.87</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A183" t="s">
         <v>228</v>
       </c>
@@ -7371,7 +7376,7 @@
         <v>3.59</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A184" s="2" t="s">
         <v>229</v>
       </c>
@@ -7400,7 +7405,7 @@
         <v>4.4800000000000004</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A185" t="s">
         <v>230</v>
       </c>
@@ -7429,7 +7434,7 @@
         <v>3.09</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A186" s="2" t="s">
         <v>231</v>
       </c>
@@ -7458,7 +7463,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A187" t="s">
         <v>232</v>
       </c>
@@ -7487,7 +7492,7 @@
         <v>2.65</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A188" s="2" t="s">
         <v>233</v>
       </c>
@@ -7516,7 +7521,7 @@
         <v>3.56</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A189" t="s">
         <v>234</v>
       </c>
@@ -7545,7 +7550,7 @@
         <v>4.47</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A190" s="2" t="s">
         <v>235</v>
       </c>
@@ -7574,7 +7579,7 @@
         <v>4.76</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A191" t="s">
         <v>236</v>
       </c>
@@ -7603,7 +7608,7 @@
         <v>3.72</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A192" s="2" t="s">
         <v>237</v>
       </c>
@@ -7632,7 +7637,7 @@
         <v>4.79</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A193" t="s">
         <v>238</v>
       </c>
@@ -7661,7 +7666,7 @@
         <v>4.76</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A194" s="2" t="s">
         <v>239</v>
       </c>
@@ -7690,7 +7695,7 @@
         <v>3.71</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A195" t="s">
         <v>240</v>
       </c>
@@ -7719,7 +7724,7 @@
         <v>3.94</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A196" s="2" t="s">
         <v>241</v>
       </c>
@@ -7748,7 +7753,7 @@
         <v>3.52</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A197" t="s">
         <v>242</v>
       </c>
@@ -7777,7 +7782,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A198" s="2" t="s">
         <v>243</v>
       </c>
@@ -7806,7 +7811,7 @@
         <v>4.58</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A199" t="s">
         <v>244</v>
       </c>
@@ -7835,7 +7840,7 @@
         <v>4.76</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A200" s="2" t="s">
         <v>245</v>
       </c>
@@ -7864,7 +7869,7 @@
         <v>3.67</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A201" t="s">
         <v>246</v>
       </c>
@@ -7893,7 +7898,7 @@
         <v>4.74</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A202" s="2" t="s">
         <v>247</v>
       </c>
@@ -7922,7 +7927,7 @@
         <v>3.47</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A203" t="s">
         <v>248</v>
       </c>
@@ -7951,7 +7956,7 @@
         <v>3.03</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A204" s="2" t="s">
         <v>249</v>
       </c>
@@ -7980,7 +7985,7 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A205" t="s">
         <v>250</v>
       </c>
@@ -8009,7 +8014,7 @@
         <v>3.94</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A206" s="2" t="s">
         <v>251</v>
       </c>
@@ -8038,7 +8043,7 @@
         <v>4.8099999999999996</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A207" t="s">
         <v>252</v>
       </c>
@@ -8067,7 +8072,7 @@
         <v>3.56</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A208" s="2" t="s">
         <v>253</v>
       </c>
@@ -8096,7 +8101,7 @@
         <v>3.83</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A209" t="s">
         <v>254</v>
       </c>
@@ -8125,7 +8130,7 @@
         <v>4.62</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A210" s="2" t="s">
         <v>255</v>
       </c>
@@ -8154,7 +8159,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A211" t="s">
         <v>256</v>
       </c>
@@ -8183,7 +8188,7 @@
         <v>3.88</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A212" s="2" t="s">
         <v>257</v>
       </c>
@@ -8212,7 +8217,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A213" t="s">
         <v>258</v>
       </c>
@@ -8241,7 +8246,7 @@
         <v>3.46</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A214" s="2" t="s">
         <v>259</v>
       </c>
@@ -8270,7 +8275,7 @@
         <v>4.47</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A215" t="s">
         <v>260</v>
       </c>
@@ -8299,7 +8304,7 @@
         <v>3.22</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A216" s="2" t="s">
         <v>261</v>
       </c>
@@ -8328,7 +8333,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A217" t="s">
         <v>262</v>
       </c>
@@ -8357,7 +8362,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A218" s="2" t="s">
         <v>263</v>
       </c>
@@ -8386,7 +8391,7 @@
         <v>4.33</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A219" t="s">
         <v>264</v>
       </c>
@@ -8415,7 +8420,7 @@
         <v>3.79</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A220" s="2" t="s">
         <v>265</v>
       </c>
@@ -8444,7 +8449,7 @@
         <v>4.16</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A221" t="s">
         <v>266</v>
       </c>
@@ -8473,7 +8478,7 @@
         <v>2.78</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A222" s="2" t="s">
         <v>267</v>
       </c>
@@ -8502,7 +8507,7 @@
         <v>4.25</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A223" t="s">
         <v>268</v>
       </c>
@@ -8531,7 +8536,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A224" s="2" t="s">
         <v>269</v>
       </c>
@@ -8560,7 +8565,7 @@
         <v>3.89</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A225" t="s">
         <v>270</v>
       </c>
@@ -8589,7 +8594,7 @@
         <v>4.05</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A226" s="2" t="s">
         <v>271</v>
       </c>
@@ -8618,7 +8623,7 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A227" t="s">
         <v>272</v>
       </c>
@@ -8647,7 +8652,7 @@
         <v>3.65</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A228" s="2" t="s">
         <v>273</v>
       </c>
@@ -8676,7 +8681,7 @@
         <v>4.1900000000000004</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A229" t="s">
         <v>274</v>
       </c>
@@ -8705,7 +8710,7 @@
         <v>3.14</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A230" s="2" t="s">
         <v>275</v>
       </c>
@@ -8734,7 +8739,7 @@
         <v>4.45</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A231" t="s">
         <v>276</v>
       </c>
@@ -8763,7 +8768,7 @@
         <v>3.42</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A232" s="2" t="s">
         <v>277</v>
       </c>
@@ -8792,7 +8797,7 @@
         <v>3.53</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A233" t="s">
         <v>278</v>
       </c>
@@ -8821,7 +8826,7 @@
         <v>3.84</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A234" s="2" t="s">
         <v>279</v>
       </c>
@@ -8850,7 +8855,7 @@
         <v>3.34</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A235" t="s">
         <v>280</v>
       </c>
@@ -8879,7 +8884,7 @@
         <v>4.46</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A236" s="2" t="s">
         <v>281</v>
       </c>
@@ -8908,7 +8913,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A237" t="s">
         <v>282</v>
       </c>
@@ -8937,7 +8942,7 @@
         <v>3.94</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A238" s="2" t="s">
         <v>283</v>
       </c>
@@ -8966,7 +8971,7 @@
         <v>4.05</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A239" t="s">
         <v>284</v>
       </c>
@@ -8995,7 +9000,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A240" s="2" t="s">
         <v>285</v>
       </c>
@@ -9024,7 +9029,7 @@
         <v>3.71</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A241" t="s">
         <v>286</v>
       </c>
@@ -9053,7 +9058,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A242" s="2" t="s">
         <v>287</v>
       </c>
@@ -9082,7 +9087,7 @@
         <v>3.32</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A243" t="s">
         <v>288</v>
       </c>
@@ -9111,7 +9116,7 @@
         <v>3.89</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A244" s="2" t="s">
         <v>289</v>
       </c>
@@ -9140,7 +9145,7 @@
         <v>4.4800000000000004</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A245" t="s">
         <v>290</v>
       </c>
@@ -9169,7 +9174,7 @@
         <v>3.44</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A246" s="2" t="s">
         <v>291</v>
       </c>
@@ -9198,7 +9203,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A247" t="s">
         <v>292</v>
       </c>
@@ -9227,7 +9232,7 @@
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A248" s="2" t="s">
         <v>293</v>
       </c>
@@ -9256,7 +9261,7 @@
         <v>4.46</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A249" t="s">
         <v>294</v>
       </c>
@@ -9285,7 +9290,7 @@
         <v>3.78</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A250" s="2" t="s">
         <v>295</v>
       </c>
@@ -9314,7 +9319,7 @@
         <v>3.58</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A251" t="s">
         <v>296</v>
       </c>
@@ -9343,7 +9348,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A252" s="2" t="s">
         <v>297</v>
       </c>
@@ -9372,7 +9377,7 @@
         <v>3.83</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A253" t="s">
         <v>298</v>
       </c>
@@ -9401,7 +9406,7 @@
         <v>3.22</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A254" s="2" t="s">
         <v>299</v>
       </c>
@@ -9430,7 +9435,7 @@
         <v>3.57</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A255" t="s">
         <v>300</v>
       </c>
@@ -9459,7 +9464,7 @@
         <v>4.63</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A256" s="2" t="s">
         <v>301</v>
       </c>
@@ -9488,7 +9493,7 @@
         <v>4.4400000000000004</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A257" t="s">
         <v>302</v>
       </c>
@@ -9517,7 +9522,7 @@
         <v>3.77</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A258" s="2" t="s">
         <v>303</v>
       </c>
@@ -9546,7 +9551,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A259" t="s">
         <v>304</v>
       </c>
@@ -9575,7 +9580,7 @@
         <v>4.4800000000000004</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A260" s="2" t="s">
         <v>305</v>
       </c>
@@ -9604,7 +9609,7 @@
         <v>4.62</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A261" t="s">
         <v>306</v>
       </c>
@@ -9633,7 +9638,7 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A262" s="2" t="s">
         <v>307</v>
       </c>
@@ -9662,7 +9667,7 @@
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A263" t="s">
         <v>308</v>
       </c>
@@ -9691,7 +9696,7 @@
         <v>4.5199999999999996</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A264" s="2" t="s">
         <v>309</v>
       </c>
@@ -9720,7 +9725,7 @@
         <v>4.63</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A265" t="s">
         <v>310</v>
       </c>
@@ -9749,7 +9754,7 @@
         <v>4.0199999999999996</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A266" s="2" t="s">
         <v>311</v>
       </c>
@@ -9778,7 +9783,7 @@
         <v>3.31</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A267" t="s">
         <v>312</v>
       </c>
@@ -9807,7 +9812,7 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A268" s="2" t="s">
         <v>313</v>
       </c>
@@ -9836,7 +9841,7 @@
         <v>3.58</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A269" t="s">
         <v>314</v>
       </c>
@@ -9865,7 +9870,7 @@
         <v>3.77</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A270" s="2" t="s">
         <v>315</v>
       </c>
@@ -9894,7 +9899,7 @@
         <v>4.03</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A271" t="s">
         <v>316</v>
       </c>
@@ -9923,7 +9928,7 @@
         <v>3.73</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A272" s="2" t="s">
         <v>317</v>
       </c>
@@ -9952,7 +9957,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A273" t="s">
         <v>318</v>
       </c>
@@ -9981,7 +9986,7 @@
         <v>4.47</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A274" s="2" t="s">
         <v>319</v>
       </c>
@@ -10010,7 +10015,7 @@
         <v>4.1900000000000004</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A275" t="s">
         <v>320</v>
       </c>
@@ -10039,7 +10044,7 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A276" s="2" t="s">
         <v>321</v>
       </c>
@@ -10068,7 +10073,7 @@
         <v>4.41</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A277" t="s">
         <v>322</v>
       </c>
@@ -10097,7 +10102,7 @@
         <v>3.48</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A278" s="2" t="s">
         <v>323</v>
       </c>
@@ -10126,7 +10131,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A279" t="s">
         <v>324</v>
       </c>
@@ -10155,7 +10160,7 @@
         <v>4.0199999999999996</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A280" s="2" t="s">
         <v>325</v>
       </c>
@@ -10184,7 +10189,7 @@
         <v>4.58</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A281" t="s">
         <v>326</v>
       </c>
@@ -10213,7 +10218,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A282" s="2" t="s">
         <v>327</v>
       </c>
@@ -10242,7 +10247,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A283" t="s">
         <v>328</v>
       </c>
@@ -10271,7 +10276,7 @@
         <v>4.74</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A284" s="2" t="s">
         <v>329</v>
       </c>
@@ -10300,7 +10305,7 @@
         <v>4.63</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A285" t="s">
         <v>330</v>
       </c>
@@ -10329,7 +10334,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A286" s="2" t="s">
         <v>331</v>
       </c>
@@ -10358,7 +10363,7 @@
         <v>3.61</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A287" t="s">
         <v>332</v>
       </c>
@@ -10387,7 +10392,7 @@
         <v>3.65</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A288" s="2" t="s">
         <v>333</v>
       </c>
@@ -10416,7 +10421,7 @@
         <v>4.6500000000000004</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A289" t="s">
         <v>334</v>
       </c>
@@ -10445,7 +10450,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A290" s="2" t="s">
         <v>335</v>
       </c>
@@ -10474,7 +10479,7 @@
         <v>3.09</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A291" t="s">
         <v>336</v>
       </c>
@@ -10503,7 +10508,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A292" s="2" t="s">
         <v>337</v>
       </c>
@@ -10532,7 +10537,7 @@
         <v>4.43</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A293" t="s">
         <v>338</v>
       </c>
@@ -10561,7 +10566,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A294" s="2" t="s">
         <v>339</v>
       </c>
@@ -10590,7 +10595,7 @@
         <v>4.1900000000000004</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A295" t="s">
         <v>340</v>
       </c>
@@ -10619,7 +10624,7 @@
         <v>2.5099999999999998</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A296" s="2" t="s">
         <v>341</v>
       </c>
@@ -10648,7 +10653,7 @@
         <v>3.51</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A297" t="s">
         <v>342</v>
       </c>
@@ -10677,7 +10682,7 @@
         <v>4.91</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A298" s="2" t="s">
         <v>343</v>
       </c>
@@ -10706,7 +10711,7 @@
         <v>4.1900000000000004</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A299" t="s">
         <v>344</v>
       </c>
@@ -10735,7 +10740,7 @@
         <v>4.32</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A300" s="2" t="s">
         <v>345</v>
       </c>
@@ -10764,7 +10769,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A301" t="s">
         <v>346</v>
       </c>
@@ -10793,7 +10798,7 @@
         <v>3.99</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A302" s="2" t="s">
         <v>347</v>
       </c>
@@ -10822,7 +10827,7 @@
         <v>4.01</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A303" t="s">
         <v>348</v>
       </c>
@@ -10851,7 +10856,7 @@
         <v>4.38</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A304" s="2" t="s">
         <v>349</v>
       </c>
@@ -10880,7 +10885,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A305" t="s">
         <v>350</v>
       </c>
@@ -10909,7 +10914,7 @@
         <v>3.16</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A306" s="2" t="s">
         <v>351</v>
       </c>
@@ -10938,7 +10943,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A307" t="s">
         <v>352</v>
       </c>
@@ -10967,7 +10972,7 @@
         <v>4.53</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A308" s="2" t="s">
         <v>353</v>
       </c>
@@ -10996,7 +11001,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A309" t="s">
         <v>354</v>
       </c>
@@ -11025,7 +11030,7 @@
         <v>3.91</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A310" s="2" t="s">
         <v>355</v>
       </c>
@@ -11054,7 +11059,7 @@
         <v>4.25</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A311" t="s">
         <v>356</v>
       </c>
@@ -11083,7 +11088,7 @@
         <v>4.62</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A312" s="2" t="s">
         <v>357</v>
       </c>
@@ -11112,7 +11117,7 @@
         <v>4.12</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A313" t="s">
         <v>358</v>
       </c>
@@ -11141,7 +11146,7 @@
         <v>4.26</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A314" s="2" t="s">
         <v>359</v>
       </c>
@@ -11170,7 +11175,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A315" t="s">
         <v>360</v>
       </c>
@@ -11199,7 +11204,7 @@
         <v>4.68</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A316" s="2" t="s">
         <v>361</v>
       </c>
@@ -11228,7 +11233,7 @@
         <v>4.09</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A317" t="s">
         <v>362</v>
       </c>
@@ -11257,7 +11262,7 @@
         <v>3.72</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A318" s="2" t="s">
         <v>363</v>
       </c>
@@ -11286,7 +11291,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A319" t="s">
         <v>364</v>
       </c>
@@ -11315,7 +11320,7 @@
         <v>3.95</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A320" s="2" t="s">
         <v>365</v>
       </c>
@@ -11344,7 +11349,7 @@
         <v>4.8899999999999997</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A321" t="s">
         <v>366</v>
       </c>
@@ -11373,7 +11378,7 @@
         <v>3.66</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A322" s="2" t="s">
         <v>367</v>
       </c>
@@ -11402,7 +11407,7 @@
         <v>3.78</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A323" t="s">
         <v>368</v>
       </c>
@@ -11431,7 +11436,7 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A324" s="2" t="s">
         <v>369</v>
       </c>
@@ -11460,7 +11465,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A325" t="s">
         <v>370</v>
       </c>
@@ -11489,7 +11494,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A326" s="2" t="s">
         <v>371</v>
       </c>
@@ -11518,7 +11523,7 @@
         <v>4.21</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A327" t="s">
         <v>372</v>
       </c>
@@ -11547,7 +11552,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A328" s="2" t="s">
         <v>373</v>
       </c>
@@ -11576,7 +11581,7 @@
         <v>3.59</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A329" t="s">
         <v>374</v>
       </c>
@@ -11605,7 +11610,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A330" s="2" t="s">
         <v>375</v>
       </c>
@@ -11634,7 +11639,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A331" t="s">
         <v>376</v>
       </c>
@@ -11663,7 +11668,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A332" s="2" t="s">
         <v>377</v>
       </c>
@@ -11692,7 +11697,7 @@
         <v>3.93</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A333" t="s">
         <v>378</v>
       </c>
@@ -11721,7 +11726,7 @@
         <v>3.19</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A334" s="2" t="s">
         <v>379</v>
       </c>
@@ -11750,7 +11755,7 @@
         <v>4.2699999999999996</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A335" t="s">
         <v>380</v>
       </c>
@@ -11779,7 +11784,7 @@
         <v>3.07</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A336" s="2" t="s">
         <v>381</v>
       </c>
@@ -11808,7 +11813,7 @@
         <v>3.99</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A337" t="s">
         <v>382</v>
       </c>
@@ -11837,7 +11842,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A338" s="2" t="s">
         <v>383</v>
       </c>
@@ -11866,7 +11871,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A339" t="s">
         <v>384</v>
       </c>
@@ -11895,7 +11900,7 @@
         <v>3.29</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A340" s="2" t="s">
         <v>385</v>
       </c>
@@ -11924,7 +11929,7 @@
         <v>3.58</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A341" t="s">
         <v>386</v>
       </c>
@@ -11953,7 +11958,7 @@
         <v>4.3600000000000003</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A342" s="2" t="s">
         <v>387</v>
       </c>
@@ -11982,7 +11987,7 @@
         <v>4.47</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A343" t="s">
         <v>388</v>
       </c>
@@ -12011,7 +12016,7 @@
         <v>3.42</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A344" s="2" t="s">
         <v>389</v>
       </c>
@@ -12040,7 +12045,7 @@
         <v>4.4800000000000004</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A345" t="s">
         <v>390</v>
       </c>
@@ -12069,7 +12074,7 @@
         <v>4.62</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A346" s="2" t="s">
         <v>391</v>
       </c>
@@ -12098,7 +12103,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A347" t="s">
         <v>392</v>
       </c>
@@ -12127,7 +12132,7 @@
         <v>4.2300000000000004</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A348" s="2" t="s">
         <v>393</v>
       </c>
@@ -12156,7 +12161,7 @@
         <v>4.24</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A349" t="s">
         <v>394</v>
       </c>
@@ -12185,7 +12190,7 @@
         <v>4.21</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A350" s="2" t="s">
         <v>395</v>
       </c>
@@ -12214,7 +12219,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A351" t="s">
         <v>396</v>
       </c>
@@ -12243,7 +12248,7 @@
         <v>3.36</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A352" s="2" t="s">
         <v>397</v>
       </c>
@@ -12272,7 +12277,7 @@
         <v>4.32</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A353" t="s">
         <v>398</v>
       </c>
@@ -12301,7 +12306,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A354" s="2" t="s">
         <v>399</v>
       </c>
@@ -12330,7 +12335,7 @@
         <v>4.41</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A355" t="s">
         <v>400</v>
       </c>
@@ -12359,7 +12364,7 @@
         <v>3.87</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A356" s="2" t="s">
         <v>401</v>
       </c>
@@ -12388,7 +12393,7 @@
         <v>3.02</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A357" t="s">
         <v>402</v>
       </c>
@@ -12417,7 +12422,7 @@
         <v>4.34</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A358" s="2" t="s">
         <v>403</v>
       </c>
@@ -12446,7 +12451,7 @@
         <v>4.34</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A359" t="s">
         <v>404</v>
       </c>
@@ -12475,7 +12480,7 @@
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A360" s="2" t="s">
         <v>405</v>
       </c>
@@ -12504,7 +12509,7 @@
         <v>4.74</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A361" t="s">
         <v>406</v>
       </c>
@@ -12533,7 +12538,7 @@
         <v>4.21</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A362" s="2" t="s">
         <v>407</v>
       </c>
@@ -12562,7 +12567,7 @@
         <v>4.46</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A363" t="s">
         <v>408</v>
       </c>
@@ -12591,7 +12596,7 @@
         <v>4.49</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A364" s="2" t="s">
         <v>409</v>
       </c>
@@ -12620,7 +12625,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A365" t="s">
         <v>410</v>
       </c>
@@ -12649,7 +12654,7 @@
         <v>3.26</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A366" s="2" t="s">
         <v>411</v>
       </c>
@@ -12678,7 +12683,7 @@
         <v>4.22</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A367" t="s">
         <v>412</v>
       </c>
@@ -12707,7 +12712,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A368" s="2" t="s">
         <v>413</v>
       </c>
@@ -12736,7 +12741,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A369" t="s">
         <v>414</v>
       </c>
@@ -12765,7 +12770,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A370" s="2" t="s">
         <v>415</v>
       </c>
@@ -12794,7 +12799,7 @@
         <v>3.86</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A371" t="s">
         <v>416</v>
       </c>
@@ -12823,7 +12828,7 @@
         <v>3.77</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A372" s="2" t="s">
         <v>417</v>
       </c>
@@ -12852,7 +12857,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A373" t="s">
         <v>418</v>
       </c>
@@ -12881,7 +12886,7 @@
         <v>3.51</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A374" s="2" t="s">
         <v>419</v>
       </c>
@@ -12910,7 +12915,7 @@
         <v>4.6900000000000004</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A375" t="s">
         <v>420</v>
       </c>
@@ -12939,7 +12944,7 @@
         <v>4.45</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A376" s="2" t="s">
         <v>421</v>
       </c>
@@ -12968,7 +12973,7 @@
         <v>3.42</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A377" t="s">
         <v>422</v>
       </c>
@@ -12997,7 +13002,7 @@
         <v>3.45</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A378" s="2" t="s">
         <v>423</v>
       </c>
@@ -13026,7 +13031,7 @@
         <v>3.08</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A379" t="s">
         <v>424</v>
       </c>
@@ -13055,7 +13060,7 @@
         <v>4.3099999999999996</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A380" s="2" t="s">
         <v>425</v>
       </c>
@@ -13084,7 +13089,7 @@
         <v>4.09</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A381" t="s">
         <v>426</v>
       </c>
@@ -13113,7 +13118,7 @@
         <v>3.43</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A382" s="2" t="s">
         <v>427</v>
       </c>
@@ -13142,7 +13147,7 @@
         <v>4.3099999999999996</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A383" t="s">
         <v>428</v>
       </c>
@@ -13171,7 +13176,7 @@
         <v>4.05</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A384" s="2" t="s">
         <v>429</v>
       </c>
@@ -13200,7 +13205,7 @@
         <v>4.6100000000000003</v>
       </c>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A385" t="s">
         <v>430</v>
       </c>
@@ -13229,7 +13234,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A386" s="2" t="s">
         <v>431</v>
       </c>
@@ -13258,7 +13263,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A387" t="s">
         <v>432</v>
       </c>
@@ -13287,7 +13292,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A388" s="2" t="s">
         <v>433</v>
       </c>
@@ -13316,7 +13321,7 @@
         <v>4.41</v>
       </c>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A389" t="s">
         <v>434</v>
       </c>
@@ -13345,7 +13350,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A390" s="2" t="s">
         <v>435</v>
       </c>
@@ -13374,7 +13379,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A391" t="s">
         <v>436</v>
       </c>
@@ -13403,7 +13408,7 @@
         <v>3.59</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A392" s="2" t="s">
         <v>437</v>
       </c>
@@ -13432,7 +13437,7 @@
         <v>4.13</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A393" t="s">
         <v>438</v>
       </c>
@@ -13461,7 +13466,7 @@
         <v>4.04</v>
       </c>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A394" s="2" t="s">
         <v>439</v>
       </c>
@@ -13490,7 +13495,7 @@
         <v>4.09</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A395" t="s">
         <v>440</v>
       </c>
@@ -13519,7 +13524,7 @@
         <v>3.61</v>
       </c>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A396" s="2" t="s">
         <v>441</v>
       </c>
@@ -13548,7 +13553,7 @@
         <v>3.43</v>
       </c>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A397" t="s">
         <v>442</v>
       </c>
@@ -13577,7 +13582,7 @@
         <v>3.74</v>
       </c>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A398" s="2" t="s">
         <v>443</v>
       </c>
@@ -13606,7 +13611,7 @@
         <v>4.92</v>
       </c>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A399" t="s">
         <v>444</v>
       </c>
@@ -13635,7 +13640,7 @@
         <v>4.22</v>
       </c>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A400" s="2" t="s">
         <v>445</v>
       </c>
@@ -13664,7 +13669,7 @@
         <v>4.05</v>
       </c>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A401" t="s">
         <v>446</v>
       </c>
@@ -13693,7 +13698,7 @@
         <v>4.13</v>
       </c>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A402" s="2" t="s">
         <v>447</v>
       </c>
@@ -13722,7 +13727,7 @@
         <v>3.46</v>
       </c>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A403" t="s">
         <v>448</v>
       </c>
@@ -13751,7 +13756,7 @@
         <v>4.04</v>
       </c>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A404" s="2" t="s">
         <v>449</v>
       </c>
@@ -13780,7 +13785,7 @@
         <v>3.51</v>
       </c>
     </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A405" t="s">
         <v>450</v>
       </c>
@@ -13809,7 +13814,7 @@
         <v>4.2300000000000004</v>
       </c>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A406" s="2" t="s">
         <v>451</v>
       </c>
@@ -13838,7 +13843,7 @@
         <v>3.93</v>
       </c>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A407" t="s">
         <v>452</v>
       </c>
@@ -13867,7 +13872,7 @@
         <v>3.13</v>
       </c>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A408" s="2" t="s">
         <v>453</v>
       </c>
@@ -13896,7 +13901,7 @@
         <v>4.33</v>
       </c>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A409" t="s">
         <v>454</v>
       </c>
@@ -13925,7 +13930,7 @@
         <v>4.29</v>
       </c>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A410" s="2" t="s">
         <v>455</v>
       </c>
@@ -13954,7 +13959,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A411" t="s">
         <v>456</v>
       </c>
@@ -13983,7 +13988,7 @@
         <v>3.95</v>
       </c>
     </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A412" s="2" t="s">
         <v>457</v>
       </c>
@@ -14012,7 +14017,7 @@
         <v>3.48</v>
       </c>
     </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A413" t="s">
         <v>458</v>
       </c>
@@ -14041,7 +14046,7 @@
         <v>3.87</v>
       </c>
     </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A414" s="2" t="s">
         <v>459</v>
       </c>
@@ -14070,7 +14075,7 @@
         <v>4.0599999999999996</v>
       </c>
     </row>
-    <row r="415" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A415" t="s">
         <v>460</v>
       </c>
@@ -14099,7 +14104,7 @@
         <v>4.54</v>
       </c>
     </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A416" s="2" t="s">
         <v>461</v>
       </c>
@@ -14128,7 +14133,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A417" t="s">
         <v>462</v>
       </c>
@@ -14157,7 +14162,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A418" s="2" t="s">
         <v>463</v>
       </c>
@@ -14186,7 +14191,7 @@
         <v>4.0199999999999996</v>
       </c>
     </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A419" t="s">
         <v>464</v>
       </c>
@@ -14215,7 +14220,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A420" s="2" t="s">
         <v>465</v>
       </c>
@@ -14244,7 +14249,7 @@
         <v>3.89</v>
       </c>
     </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A421" t="s">
         <v>466</v>
       </c>
@@ -14273,7 +14278,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A422" s="2" t="s">
         <v>467</v>
       </c>
@@ -14302,7 +14307,7 @@
         <v>3.49</v>
       </c>
     </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A423" t="s">
         <v>468</v>
       </c>
@@ -14331,7 +14336,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A424" s="2" t="s">
         <v>469</v>
       </c>
@@ -14360,7 +14365,7 @@
         <v>3.93</v>
       </c>
     </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A425" t="s">
         <v>470</v>
       </c>
@@ -14389,7 +14394,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="426" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A426" s="2" t="s">
         <v>471</v>
       </c>
@@ -14418,7 +14423,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="427" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A427" t="s">
         <v>472</v>
       </c>
@@ -14447,7 +14452,7 @@
         <v>3.94</v>
       </c>
     </row>
-    <row r="428" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A428" s="2" t="s">
         <v>473</v>
       </c>
@@ -14476,7 +14481,7 @@
         <v>4.63</v>
       </c>
     </row>
-    <row r="429" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A429" t="s">
         <v>474</v>
       </c>
@@ -14505,7 +14510,7 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A430" s="2" t="s">
         <v>475</v>
       </c>
@@ -14534,7 +14539,7 @@
         <v>3.67</v>
       </c>
     </row>
-    <row r="431" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A431" t="s">
         <v>476</v>
       </c>
@@ -14563,7 +14568,7 @@
         <v>4.91</v>
       </c>
     </row>
-    <row r="432" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A432" s="2" t="s">
         <v>477</v>
       </c>
@@ -14592,7 +14597,7 @@
         <v>4.68</v>
       </c>
     </row>
-    <row r="433" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A433" t="s">
         <v>478</v>
       </c>
@@ -14621,7 +14626,7 @@
         <v>3.38</v>
       </c>
     </row>
-    <row r="434" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A434" s="2" t="s">
         <v>479</v>
       </c>
@@ -14650,7 +14655,7 @@
         <v>4.08</v>
       </c>
     </row>
-    <row r="435" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A435" t="s">
         <v>480</v>
       </c>
@@ -14679,7 +14684,7 @@
         <v>4.51</v>
       </c>
     </row>
-    <row r="436" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A436" s="2" t="s">
         <v>481</v>
       </c>
@@ -14708,7 +14713,7 @@
         <v>3.93</v>
       </c>
     </row>
-    <row r="437" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A437" t="s">
         <v>482</v>
       </c>
@@ -14737,7 +14742,7 @@
         <v>4.13</v>
       </c>
     </row>
-    <row r="438" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A438" s="2" t="s">
         <v>483</v>
       </c>
@@ -14766,7 +14771,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="439" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A439" t="s">
         <v>484</v>
       </c>
@@ -14795,7 +14800,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="440" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A440" s="2" t="s">
         <v>485</v>
       </c>
@@ -14824,7 +14829,7 @@
         <v>3.74</v>
       </c>
     </row>
-    <row r="441" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A441" t="s">
         <v>486</v>
       </c>
@@ -14853,7 +14858,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="442" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A442" s="2" t="s">
         <v>487</v>
       </c>
@@ -14882,7 +14887,7 @@
         <v>4.46</v>
       </c>
     </row>
-    <row r="443" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A443" t="s">
         <v>488</v>
       </c>
@@ -14911,7 +14916,7 @@
         <v>4.91</v>
       </c>
     </row>
-    <row r="444" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A444" s="2" t="s">
         <v>489</v>
       </c>
@@ -14940,7 +14945,7 @@
         <v>3.36</v>
       </c>
     </row>
-    <row r="445" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A445" t="s">
         <v>490</v>
       </c>
@@ -14969,7 +14974,7 @@
         <v>4.41</v>
       </c>
     </row>
-    <row r="446" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A446" s="2" t="s">
         <v>491</v>
       </c>
@@ -14998,7 +15003,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="447" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A447" t="s">
         <v>492</v>
       </c>
@@ -15027,7 +15032,7 @@
         <v>4.7300000000000004</v>
       </c>
     </row>
-    <row r="448" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A448" s="2" t="s">
         <v>493</v>
       </c>
@@ -15056,7 +15061,7 @@
         <v>3.53</v>
       </c>
     </row>
-    <row r="449" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A449" t="s">
         <v>494</v>
       </c>
@@ -15085,7 +15090,7 @@
         <v>4.95</v>
       </c>
     </row>
-    <row r="450" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A450" s="2" t="s">
         <v>495</v>
       </c>
@@ -15114,7 +15119,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="451" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A451" t="s">
         <v>496</v>
       </c>
@@ -15143,7 +15148,7 @@
         <v>4.3899999999999997</v>
       </c>
     </row>
-    <row r="452" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A452" s="2" t="s">
         <v>497</v>
       </c>
@@ -15172,7 +15177,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="453" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A453" t="s">
         <v>498</v>
       </c>
@@ -15201,7 +15206,7 @@
         <v>4.05</v>
       </c>
     </row>
-    <row r="454" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A454" s="2" t="s">
         <v>499</v>
       </c>
@@ -15230,7 +15235,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="455" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A455" t="s">
         <v>500</v>
       </c>
@@ -15259,7 +15264,7 @@
         <v>3.71</v>
       </c>
     </row>
-    <row r="456" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A456" s="2" t="s">
         <v>501</v>
       </c>
@@ -15288,7 +15293,7 @@
         <v>4.24</v>
       </c>
     </row>
-    <row r="457" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A457" t="s">
         <v>502</v>
       </c>
@@ -15317,7 +15322,7 @@
         <v>4.83</v>
       </c>
     </row>
-    <row r="458" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A458" s="2" t="s">
         <v>503</v>
       </c>
@@ -15346,7 +15351,7 @@
         <v>3.59</v>
       </c>
     </row>
-    <row r="459" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A459" t="s">
         <v>504</v>
       </c>
@@ -15375,7 +15380,7 @@
         <v>3.16</v>
       </c>
     </row>
-    <row r="460" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A460" s="2" t="s">
         <v>505</v>
       </c>
@@ -15404,7 +15409,7 @@
         <v>4.07</v>
       </c>
     </row>
-    <row r="461" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A461" t="s">
         <v>506</v>
       </c>
@@ -15433,7 +15438,7 @@
         <v>3.93</v>
       </c>
     </row>
-    <row r="462" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A462" s="2" t="s">
         <v>507</v>
       </c>
@@ -15462,7 +15467,7 @@
         <v>4.01</v>
       </c>
     </row>
-    <row r="463" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A463" t="s">
         <v>508</v>
       </c>
@@ -15491,7 +15496,7 @@
         <v>4.9400000000000004</v>
       </c>
     </row>
-    <row r="464" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A464" s="2" t="s">
         <v>509</v>
       </c>
@@ -15520,7 +15525,7 @@
         <v>4.6100000000000003</v>
       </c>
     </row>
-    <row r="465" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A465" t="s">
         <v>510</v>
       </c>
@@ -15549,7 +15554,7 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="466" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A466" s="2" t="s">
         <v>511</v>
       </c>
@@ -15578,7 +15583,7 @@
         <v>4.62</v>
       </c>
     </row>
-    <row r="467" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A467" t="s">
         <v>512</v>
       </c>
@@ -15607,7 +15612,7 @@
         <v>4.53</v>
       </c>
     </row>
-    <row r="468" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A468" s="2" t="s">
         <v>513</v>
       </c>
@@ -15636,7 +15641,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="469" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A469" t="s">
         <v>514</v>
       </c>
@@ -15665,7 +15670,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="470" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A470" s="2" t="s">
         <v>515</v>
       </c>
@@ -15694,7 +15699,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="471" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A471" t="s">
         <v>516</v>
       </c>
@@ -15723,7 +15728,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="472" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A472" s="2" t="s">
         <v>517</v>
       </c>
@@ -15752,7 +15757,7 @@
         <v>4.01</v>
       </c>
     </row>
-    <row r="473" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A473" t="s">
         <v>518</v>
       </c>
@@ -15781,7 +15786,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="474" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A474" s="2" t="s">
         <v>519</v>
       </c>
@@ -15810,7 +15815,7 @@
         <v>4.66</v>
       </c>
     </row>
-    <row r="475" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A475" t="s">
         <v>520</v>
       </c>
@@ -15839,7 +15844,7 @@
         <v>4.59</v>
       </c>
     </row>
-    <row r="476" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A476" s="2" t="s">
         <v>521</v>
       </c>
@@ -15868,7 +15873,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="477" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A477" t="s">
         <v>522</v>
       </c>
@@ -15897,7 +15902,7 @@
         <v>3.68</v>
       </c>
     </row>
-    <row r="478" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A478" s="2" t="s">
         <v>523</v>
       </c>
@@ -15926,7 +15931,7 @@
         <v>4.6900000000000004</v>
       </c>
     </row>
-    <row r="479" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A479" t="s">
         <v>524</v>
       </c>
@@ -15955,7 +15960,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="480" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A480" s="2" t="s">
         <v>525</v>
       </c>
@@ -15984,7 +15989,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="481" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A481" t="s">
         <v>526</v>
       </c>
@@ -16013,7 +16018,7 @@
         <v>3.28</v>
       </c>
     </row>
-    <row r="482" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A482" s="2" t="s">
         <v>527</v>
       </c>
@@ -16042,7 +16047,7 @@
         <v>4.63</v>
       </c>
     </row>
-    <row r="483" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A483" t="s">
         <v>528</v>
       </c>
@@ -16071,7 +16076,7 @@
         <v>3.78</v>
       </c>
     </row>
-    <row r="484" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A484" s="2" t="s">
         <v>529</v>
       </c>
@@ -16100,7 +16105,7 @@
         <v>3.76</v>
       </c>
     </row>
-    <row r="485" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A485" t="s">
         <v>530</v>
       </c>
@@ -16129,7 +16134,7 @@
         <v>3.72</v>
       </c>
     </row>
-    <row r="486" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A486" s="2" t="s">
         <v>531</v>
       </c>
@@ -16158,7 +16163,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="487" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A487" t="s">
         <v>532</v>
       </c>
@@ -16187,7 +16192,7 @@
         <v>4.76</v>
       </c>
     </row>
-    <row r="488" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A488" s="2" t="s">
         <v>533</v>
       </c>
@@ -16216,7 +16221,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="489" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A489" t="s">
         <v>534</v>
       </c>
@@ -16245,7 +16250,7 @@
         <v>4.04</v>
       </c>
     </row>
-    <row r="490" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A490" s="2" t="s">
         <v>535</v>
       </c>
@@ -16274,7 +16279,7 @@
         <v>4.58</v>
       </c>
     </row>
-    <row r="491" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A491" t="s">
         <v>536</v>
       </c>
@@ -16303,7 +16308,7 @@
         <v>4.32</v>
       </c>
     </row>
-    <row r="492" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A492" s="2" t="s">
         <v>537</v>
       </c>
@@ -16332,7 +16337,7 @@
         <v>3.99</v>
       </c>
     </row>
-    <row r="493" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A493" t="s">
         <v>538</v>
       </c>
@@ -16361,7 +16366,7 @@
         <v>3.62</v>
       </c>
     </row>
-    <row r="494" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A494" s="2" t="s">
         <v>539</v>
       </c>
@@ -16390,7 +16395,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="495" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A495" t="s">
         <v>540</v>
       </c>
@@ -16419,7 +16424,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="496" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A496" s="2" t="s">
         <v>541</v>
       </c>
@@ -16448,7 +16453,7 @@
         <v>3.15</v>
       </c>
     </row>
-    <row r="497" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A497" t="s">
         <v>542</v>
       </c>
@@ -16477,7 +16482,7 @@
         <v>4.08</v>
       </c>
     </row>
-    <row r="498" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A498" s="2" t="s">
         <v>543</v>
       </c>
@@ -16506,7 +16511,7 @@
         <v>4.38</v>
       </c>
     </row>
-    <row r="499" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A499" t="s">
         <v>544</v>
       </c>
@@ -16535,7 +16540,7 @@
         <v>3.74</v>
       </c>
     </row>
-    <row r="500" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A500" s="2" t="s">
         <v>545</v>
       </c>
@@ -16564,7 +16569,7 @@
         <v>4.59</v>
       </c>
     </row>
-    <row r="501" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A501" t="s">
         <v>546</v>
       </c>
@@ -16596,5 +16601,6 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>